--- a/inasistencias-5b-Tec-Dig/alumnos-5b-Tec-Dig.xlsx
+++ b/inasistencias-5b-Tec-Dig/alumnos-5b-Tec-Dig.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="asistencia" sheetId="1" state="visible" r:id="rId3"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1629" uniqueCount="344">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1633" uniqueCount="345">
   <si>
     <t xml:space="preserve">total</t>
   </si>
@@ -358,6 +358,9 @@
   </si>
   <si>
     <t xml:space="preserve">Diciebre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Diciembre</t>
   </si>
   <si>
     <t xml:space="preserve">1-codigos</t>
@@ -1171,7 +1174,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1237,6 +1240,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1574,6 +1581,7 @@
     <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="59" min="45" style="1" width="8.99"/>
     <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="62" min="60" style="2" width="8.99"/>
     <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="66" min="63" style="1" width="8.99"/>
+    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="67" min="67" style="0" width="8.99"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1589,7 +1597,9 @@
       <c r="BR1" s="4" t="n">
         <v>46001</v>
       </c>
-      <c r="BS1" s="1"/>
+      <c r="BS1" s="4" t="n">
+        <v>46003</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
@@ -3378,6 +3388,9 @@
       <c r="BR11" s="11" t="s">
         <v>19</v>
       </c>
+      <c r="BS11" s="11" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="n">
@@ -4436,6 +4449,9 @@
       <c r="BR17" s="11" t="s">
         <v>20</v>
       </c>
+      <c r="BS17" s="11" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="n">
@@ -4800,6 +4816,9 @@
       </c>
       <c r="BR19" s="11" t="s">
         <v>19</v>
+      </c>
+      <c r="BS19" s="11" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6288,7 +6307,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:AC26"/>
+  <dimension ref="A1:AD26"/>
   <sheetFormatPr defaultColWidth="9.796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4.2"/>
@@ -6296,7 +6315,8 @@
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="10" min="3" style="1" width="9.39"/>
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="11" min="11" style="1" width="9.56"/>
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="13" min="12" style="1" width="9.58"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="22" min="14" style="1" width="9.79"/>
+    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="22" min="14" style="1" width="9.79"/>
+    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="29" min="23" style="0" width="9.79"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6317,6 +6337,9 @@
       <c r="AA1" s="1"/>
       <c r="AB1" s="1"/>
       <c r="AC1" s="1"/>
+      <c r="AD1" s="17" t="s">
+        <v>110</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
@@ -6326,85 +6349,85 @@
         <v>3</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="K2" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="N2" s="1" t="s">
         <v>118</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>117</v>
       </c>
       <c r="O2" s="4" t="n">
         <v>45856</v>
       </c>
       <c r="P2" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="Q2" s="16" t="s">
+        <v>123</v>
+      </c>
+      <c r="R2" s="16" t="s">
+        <v>124</v>
+      </c>
+      <c r="S2" s="16" t="s">
+        <v>125</v>
+      </c>
+      <c r="T2" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="Q2" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="R2" s="16" t="s">
-        <v>123</v>
-      </c>
-      <c r="S2" s="16" t="s">
-        <v>124</v>
-      </c>
-      <c r="T2" s="3" t="s">
-        <v>120</v>
-      </c>
       <c r="U2" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="V2" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="W2" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="X2" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="Y2" s="16" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="Z2" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="AA2" s="1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="AB2" s="16" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="AC2" s="16" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6912,10 +6935,10 @@
       <c r="E9" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="F9" s="17" t="n">
-        <v>9</v>
-      </c>
-      <c r="G9" s="18" t="n">
+      <c r="F9" s="18" t="n">
+        <v>9</v>
+      </c>
+      <c r="G9" s="19" t="n">
         <v>45784</v>
       </c>
       <c r="H9" s="1" t="n">
@@ -7132,6 +7155,9 @@
       <c r="X11" s="2" t="n">
         <v>6</v>
       </c>
+      <c r="AD11" s="11" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="n">
@@ -7149,13 +7175,13 @@
       <c r="E12" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="F12" s="17" t="n">
+      <c r="F12" s="18" t="n">
         <v>7</v>
       </c>
-      <c r="G12" s="18" t="n">
+      <c r="G12" s="19" t="n">
         <v>45856</v>
       </c>
-      <c r="H12" s="17" t="n">
+      <c r="H12" s="18" t="n">
         <v>23</v>
       </c>
       <c r="I12" s="1" t="n">
@@ -7633,6 +7659,9 @@
       <c r="AB17" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="AD17" s="11" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="n">
@@ -7802,6 +7831,9 @@
       </c>
       <c r="AB19" s="2" t="n">
         <v>1</v>
+      </c>
+      <c r="AD19" s="11" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8378,16 +8410,16 @@
         <v>45751</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G1" s="6" t="s">
         <v>13</v>
       </c>
       <c r="H1" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="I1" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="J1" s="6"/>
       <c r="K1" s="6"/>
@@ -8932,22 +8964,22 @@
         <v>3</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8961,10 +8993,10 @@
         <v>17</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F2" s="1" t="n">
         <v>9</v>
@@ -8984,10 +9016,10 @@
         <v>22</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F3" s="1" t="n">
         <v>8</v>
@@ -9007,10 +9039,10 @@
         <v>27</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F4" s="1" t="n">
         <v>8</v>
@@ -9030,10 +9062,10 @@
         <v>33</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F5" s="1" t="n">
         <v>10</v>
@@ -9053,10 +9085,10 @@
         <v>40</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F6" s="1" t="n">
         <v>9</v>
@@ -9076,10 +9108,10 @@
         <v>43</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F7" s="1" t="n">
         <v>9</v>
@@ -9099,10 +9131,10 @@
         <v>46</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F8" s="1" t="n">
         <v>9</v>
@@ -9122,10 +9154,10 @@
         <v>50</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F9" s="1" t="n">
         <v>9</v>
@@ -9145,10 +9177,10 @@
         <v>57</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F10" s="1" t="n">
         <v>9</v>
@@ -9182,10 +9214,10 @@
         <v>64</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F12" s="1" t="n">
         <v>10</v>
@@ -9205,10 +9237,10 @@
         <v>67</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F13" s="1" t="n">
         <v>8</v>
@@ -9228,10 +9260,10 @@
         <v>70</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F14" s="1" t="n">
         <v>9</v>
@@ -9251,10 +9283,10 @@
         <v>73</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F15" s="1" t="n">
         <v>10</v>
@@ -9274,10 +9306,10 @@
         <v>77</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F16" s="1" t="n">
         <v>4</v>
@@ -9297,10 +9329,10 @@
         <v>81</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F17" s="1" t="n">
         <v>9</v>
@@ -9320,10 +9352,10 @@
         <v>84</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F18" s="1" t="n">
         <v>10</v>
@@ -9343,10 +9375,10 @@
         <v>87</v>
       </c>
       <c r="D19" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="E19" s="1" t="s">
         <v>169</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>168</v>
       </c>
       <c r="F19" s="1" t="n">
         <v>9</v>
@@ -9366,10 +9398,10 @@
         <v>90</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F20" s="1" t="n">
         <v>9</v>
@@ -9391,10 +9423,10 @@
         <v>90</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F21" s="1" t="n">
         <v>9</v>
@@ -9405,10 +9437,10 @@
         <v>90</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F22" s="1" t="n">
         <v>2</v>
@@ -9425,10 +9457,10 @@
         <v>93</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F23" s="1" t="n">
         <v>10</v>
@@ -9448,10 +9480,10 @@
         <v>96</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F24" s="1" t="n">
         <v>10</v>
@@ -9471,10 +9503,10 @@
         <v>99</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F25" s="1" t="n">
         <v>10</v>
@@ -9494,10 +9526,10 @@
         <v>102</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F26" s="1" t="n">
         <v>10</v>
@@ -9536,13 +9568,13 @@
         <v>3</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9556,10 +9588,10 @@
         <v>17</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F2" s="1" t="n">
         <v>10</v>
@@ -9576,10 +9608,10 @@
         <v>22</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F3" s="1" t="n">
         <v>8</v>
@@ -9596,10 +9628,10 @@
         <v>27</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F4" s="1" t="n">
         <v>9</v>
@@ -9616,10 +9648,10 @@
         <v>33</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F5" s="1" t="n">
         <v>9</v>
@@ -9636,10 +9668,10 @@
         <v>40</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F6" s="1" t="n">
         <v>10</v>
@@ -9656,10 +9688,10 @@
         <v>43</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F7" s="1" t="n">
         <v>10</v>
@@ -9676,10 +9708,10 @@
         <v>46</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F8" s="1" t="n">
         <v>9</v>
@@ -9696,10 +9728,10 @@
         <v>50</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F9" s="1" t="n">
         <v>10</v>
@@ -9716,10 +9748,10 @@
         <v>57</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F10" s="1" t="n">
         <v>10</v>
@@ -9736,10 +9768,10 @@
         <v>60</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F11" s="1" t="n">
         <v>10</v>
@@ -9756,10 +9788,10 @@
         <v>64</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F12" s="1" t="n">
         <v>10</v>
@@ -9776,10 +9808,10 @@
         <v>67</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F13" s="1" t="n">
         <v>10</v>
@@ -9796,10 +9828,10 @@
         <v>70</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F14" s="1" t="n">
         <v>10</v>
@@ -9816,10 +9848,10 @@
         <v>73</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F15" s="1" t="n">
         <v>10</v>
@@ -9836,10 +9868,10 @@
         <v>77</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F16" s="1" t="n">
         <v>10</v>
@@ -9856,10 +9888,10 @@
         <v>81</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F17" s="1" t="n">
         <v>10</v>
@@ -9876,10 +9908,10 @@
         <v>84</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F18" s="1" t="n">
         <v>7</v>
@@ -9896,10 +9928,10 @@
         <v>87</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F19" s="1" t="n">
         <v>10</v>
@@ -9916,10 +9948,10 @@
         <v>90</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F20" s="1" t="n">
         <v>10</v>
@@ -9936,10 +9968,10 @@
         <v>93</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F21" s="1" t="n">
         <v>9</v>
@@ -9956,10 +9988,10 @@
         <v>96</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F22" s="1" t="n">
         <v>9</v>
@@ -9976,10 +10008,10 @@
         <v>99</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F23" s="1" t="n">
         <v>10</v>
@@ -9996,10 +10028,10 @@
         <v>102</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F24" s="1" t="n">
         <v>9</v>
@@ -10036,22 +10068,22 @@
         <v>3</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10065,10 +10097,10 @@
         <v>17</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F2" s="1" t="n">
         <v>8</v>
@@ -10088,10 +10120,10 @@
         <v>22</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F3" s="1" t="n">
         <v>9</v>
@@ -10111,10 +10143,10 @@
         <v>27</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F4" s="1" t="n">
         <v>10</v>
@@ -10134,10 +10166,10 @@
         <v>33</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F5" s="1" t="n">
         <v>10</v>
@@ -10157,10 +10189,10 @@
         <v>40</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F6" s="1" t="n">
         <v>10</v>
@@ -10180,10 +10212,10 @@
         <v>43</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F7" s="1" t="n">
         <v>10</v>
@@ -10203,10 +10235,10 @@
         <v>46</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F8" s="1" t="n">
         <v>10</v>
@@ -10226,10 +10258,10 @@
         <v>50</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F9" s="1" t="n">
         <v>10</v>
@@ -10249,10 +10281,10 @@
         <v>57</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F10" s="1" t="n">
         <v>10</v>
@@ -10286,10 +10318,10 @@
         <v>64</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F12" s="1" t="n">
         <v>9</v>
@@ -10309,10 +10341,10 @@
         <v>67</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="F13" s="1" t="n">
         <v>8</v>
@@ -10332,10 +10364,10 @@
         <v>70</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F14" s="1" t="n">
         <v>10</v>
@@ -10357,10 +10389,10 @@
         <v>70</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F15" s="1" t="n">
         <v>10</v>
@@ -10371,10 +10403,10 @@
         <v>70</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F16" s="1" t="n">
         <v>9</v>
@@ -10391,10 +10423,10 @@
         <v>73</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F17" s="1" t="n">
         <v>8</v>
@@ -10414,10 +10446,10 @@
         <v>77</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F18" s="1" t="n">
         <v>7</v>
@@ -10437,10 +10469,10 @@
         <v>81</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F19" s="1" t="n">
         <v>10</v>
@@ -10460,10 +10492,10 @@
         <v>84</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F20" s="1" t="n">
         <v>8</v>
@@ -10483,10 +10515,10 @@
         <v>87</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F21" s="1" t="n">
         <v>9</v>
@@ -10506,10 +10538,10 @@
         <v>90</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F22" s="1" t="n">
         <v>7</v>
@@ -10529,10 +10561,10 @@
         <v>93</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F23" s="1" t="n">
         <v>10</v>
@@ -10552,10 +10584,10 @@
         <v>96</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F24" s="1" t="n">
         <v>0</v>
@@ -10575,10 +10607,10 @@
         <v>99</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F25" s="1" t="n">
         <v>10</v>
@@ -10598,10 +10630,10 @@
         <v>102</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F26" s="1" t="n">
         <v>9</v>
@@ -10612,7 +10644,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H27" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
   </sheetData>
@@ -10646,22 +10678,22 @@
         <v>3</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10675,10 +10707,10 @@
         <v>17</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F2" s="1" t="n">
         <v>8</v>
@@ -10698,10 +10730,10 @@
         <v>22</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F3" s="1" t="n">
         <v>6</v>
@@ -10723,10 +10755,10 @@
         <v>22</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F4" s="1" t="n">
         <v>6</v>
@@ -10743,10 +10775,10 @@
         <v>27</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F5" s="1" t="n">
         <v>10</v>
@@ -10822,10 +10854,10 @@
         <v>50</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F10" s="1" t="n">
         <v>10</v>
@@ -10845,10 +10877,10 @@
         <v>57</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="F11" s="1" t="n">
         <v>6</v>
@@ -10882,10 +10914,10 @@
         <v>64</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F13" s="1" t="n">
         <v>9</v>
@@ -10919,10 +10951,10 @@
         <v>70</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F15" s="1" t="n">
         <v>10</v>
@@ -10998,10 +11030,10 @@
         <v>87</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="F20" s="1" t="n">
         <v>10</v>
@@ -11063,10 +11095,10 @@
         <v>99</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="F24" s="1" t="n">
         <v>10</v>
@@ -11086,10 +11118,10 @@
         <v>102</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F25" s="1" t="n">
         <v>6</v>
@@ -11127,22 +11159,22 @@
         <v>3</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11150,10 +11182,10 @@
         <v>22</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="D2" s="1" t="n">
         <v>8</v>
@@ -11175,10 +11207,10 @@
         <v>22</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="D3" s="1" t="n">
         <v>8</v>
@@ -11189,10 +11221,10 @@
         <v>22</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D4" s="1" t="n">
         <v>6</v>
@@ -11203,10 +11235,10 @@
         <v>22</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D5" s="1" t="n">
         <v>5</v>
@@ -11217,10 +11249,10 @@
         <v>40</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D6" s="1" t="n">
         <v>8</v>
@@ -11242,10 +11274,10 @@
         <v>40</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="D7" s="1" t="n">
         <v>8</v>
@@ -11256,10 +11288,10 @@
         <v>40</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D8" s="1" t="n">
         <v>8</v>
@@ -11270,10 +11302,10 @@
         <v>40</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D9" s="1" t="n">
         <v>7</v>
@@ -11284,10 +11316,10 @@
         <v>40</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="D10" s="1" t="n">
         <v>7</v>
@@ -11298,10 +11330,10 @@
         <v>40</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="D11" s="1" t="n">
         <v>5</v>
@@ -11312,10 +11344,10 @@
         <v>40</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="D12" s="1" t="n">
         <v>4</v>
@@ -11326,10 +11358,10 @@
         <v>40</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D13" s="1" t="n">
         <v>3</v>
@@ -11340,10 +11372,10 @@
         <v>43</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="D14" s="1" t="n">
         <v>8</v>
@@ -11365,10 +11397,10 @@
         <v>43</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="D15" s="1" t="n">
         <v>6</v>
@@ -11379,10 +11411,10 @@
         <v>67</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D16" s="1" t="n">
         <v>7</v>
@@ -11404,10 +11436,10 @@
         <v>67</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="D17" s="1" t="n">
         <v>3</v>
@@ -11418,10 +11450,10 @@
         <v>73</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D18" s="1" t="n">
         <v>8</v>
@@ -11443,10 +11475,10 @@
         <v>73</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="D19" s="1" t="n">
         <v>7</v>
@@ -11457,10 +11489,10 @@
         <v>73</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="D20" s="1" t="n">
         <v>3</v>
@@ -11471,10 +11503,10 @@
         <v>84</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="D21" s="1" t="n">
         <v>7</v>
@@ -11488,10 +11520,10 @@
         <v>90</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="D22" s="1" t="n">
         <v>8</v>
@@ -11505,10 +11537,10 @@
         <v>96</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="D23" s="1" t="n">
         <v>6</v>
@@ -11550,10 +11582,10 @@
         <v>2</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11570,7 +11602,7 @@
         <v>16</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="F2" s="1" t="n">
         <v>9.25</v>
@@ -11590,7 +11622,7 @@
         <v>21</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="F3" s="1" t="n">
         <v>9</v>
@@ -11610,7 +11642,7 @@
         <v>26</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="F4" s="1" t="n">
         <v>10</v>
@@ -11630,7 +11662,7 @@
         <v>32</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="F5" s="1" t="n">
         <v>9.5</v>
@@ -11650,7 +11682,7 @@
         <v>39</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F6" s="1" t="n">
         <v>8.75</v>
@@ -11670,7 +11702,7 @@
         <v>42</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="F7" s="1" t="n">
         <v>9.75</v>
@@ -11690,7 +11722,7 @@
         <v>45</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="F8" s="1" t="n">
         <v>9.75</v>
@@ -11710,7 +11742,7 @@
         <v>49</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="F9" s="1" t="n">
         <v>10</v>
@@ -11730,7 +11762,7 @@
         <v>56</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="F10" s="1" t="n">
         <v>8.75</v>
@@ -11750,7 +11782,7 @@
         <v>59</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="F11" s="1" t="n">
         <v>4.5</v>
@@ -11770,7 +11802,7 @@
         <v>63</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="F12" s="1" t="n">
         <v>8.75</v>
@@ -11790,7 +11822,7 @@
         <v>66</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="F13" s="1" t="n">
         <v>9</v>
@@ -11810,7 +11842,7 @@
         <v>69</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="F14" s="1" t="n">
         <v>10</v>
@@ -11830,7 +11862,7 @@
         <v>72</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="F15" s="1" t="n">
         <v>8</v>
@@ -11850,7 +11882,7 @@
         <v>76</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F16" s="1" t="n">
         <v>8</v>
@@ -11870,7 +11902,7 @@
         <v>80</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="F17" s="1" t="n">
         <v>8.75</v>
@@ -11890,7 +11922,7 @@
         <v>83</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="F18" s="1" t="n">
         <v>8.75</v>
@@ -11910,7 +11942,7 @@
         <v>86</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="F19" s="1" t="n">
         <v>9.5</v>
@@ -11930,7 +11962,7 @@
         <v>89</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="F20" s="1" t="n">
         <v>8.75</v>
@@ -11950,7 +11982,7 @@
         <v>92</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="F21" s="1" t="n">
         <v>8.25</v>
@@ -11970,7 +12002,7 @@
         <v>95</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="F22" s="1" t="n">
         <v>8.75</v>
@@ -11990,7 +12022,7 @@
         <v>98</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="F23" s="1" t="n">
         <v>4.25</v>
@@ -12010,7 +12042,7 @@
         <v>101</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="F24" s="1" t="n">
         <v>7</v>
